--- a/artfynd/A 44406-2021 artfynd.xlsx
+++ b/artfynd/A 44406-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115984543</v>
+        <v>115984449</v>
       </c>
       <c r="B2" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525391</v>
+        <v>525146</v>
       </c>
       <c r="R2" t="n">
-        <v>7264580</v>
+        <v>7264654</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,7 +759,7 @@
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115984707</v>
+        <v>115984458</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,39 +792,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525207</v>
+        <v>525168</v>
       </c>
       <c r="R3" t="n">
-        <v>7264450</v>
+        <v>7264635</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -869,11 +854,6 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -885,7 +865,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -907,55 +887,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115984447</v>
+        <v>115984465</v>
       </c>
       <c r="B4" t="n">
-        <v>5165</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525143</v>
+        <v>525382</v>
       </c>
       <c r="R4" t="n">
-        <v>7264657</v>
+        <v>7264626</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1001,7 +971,7 @@
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1023,54 +993,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115984537</v>
+        <v>115984509</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525477</v>
+        <v>525296</v>
       </c>
       <c r="R5" t="n">
-        <v>7264582</v>
+        <v>7264594</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1116,7 +1077,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1138,37 +1099,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115984480</v>
+        <v>115984543</v>
       </c>
       <c r="B6" t="n">
-        <v>89035</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1599</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525369</v>
+        <v>525391</v>
       </c>
       <c r="R6" t="n">
-        <v>7264614</v>
+        <v>7264580</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1227,7 +1183,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1249,15 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115984570</v>
+        <v>115984566</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1289,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>525525</v>
+        <v>525238</v>
       </c>
       <c r="R7" t="n">
-        <v>7264567</v>
+        <v>7264568</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1338,7 +1289,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3442</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1360,55 +1311,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115984460</v>
+        <v>115984453</v>
       </c>
       <c r="B8" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>918</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>525225</v>
+        <v>525177</v>
       </c>
       <c r="R8" t="n">
-        <v>7264633</v>
+        <v>7264639</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1443,11 +1384,6 @@
           <t>2022-09-22</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>färska hackmärken</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1459,7 +1395,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1481,15 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115984453</v>
+        <v>115984461</v>
       </c>
       <c r="B9" t="n">
-        <v>91117</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1521,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525177</v>
+        <v>525246</v>
       </c>
       <c r="R9" t="n">
-        <v>7264639</v>
+        <v>7264629</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1570,7 +1501,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>3431</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1592,37 +1523,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115984558</v>
+        <v>115984553</v>
       </c>
       <c r="B10" t="n">
-        <v>90341</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>918</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1632,10 +1558,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525234</v>
+        <v>525220</v>
       </c>
       <c r="R10" t="n">
-        <v>7264571</v>
+        <v>7264572</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1681,7 +1607,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3440</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1703,37 +1629,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115984579</v>
+        <v>115984591</v>
       </c>
       <c r="B11" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3298</v>
+        <v>918</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,10 +1664,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>525543</v>
+        <v>525546</v>
       </c>
       <c r="R11" t="n">
-        <v>7264552</v>
+        <v>7264537</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1792,7 +1713,7 @@
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1814,15 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115984602</v>
+        <v>115984679</v>
       </c>
       <c r="B12" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1830,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1854,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>525541</v>
+        <v>525214</v>
       </c>
       <c r="R12" t="n">
-        <v>7264532</v>
+        <v>7264470</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1903,7 +1819,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>3484</t>
+          <t>3535</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1925,15 +1841,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115984449</v>
+        <v>115984558</v>
       </c>
       <c r="B13" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,21 +1852,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1965,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>525146</v>
+        <v>525234</v>
       </c>
       <c r="R13" t="n">
-        <v>7264654</v>
+        <v>7264571</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2014,7 +1925,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2036,37 +1947,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115984566</v>
+        <v>115984560</v>
       </c>
       <c r="B14" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2076,10 +1982,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>525238</v>
+        <v>525217</v>
       </c>
       <c r="R14" t="n">
-        <v>7264568</v>
+        <v>7264571</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2125,7 +2031,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2150,16 +2056,11 @@
         <v>115984456</v>
       </c>
       <c r="B15" t="n">
-        <v>90783</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2172,12 +2073,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2258,37 +2159,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115984492</v>
+        <v>115984554</v>
       </c>
       <c r="B16" t="n">
-        <v>91272</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,10 +2194,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>525382</v>
+        <v>525188</v>
       </c>
       <c r="R16" t="n">
-        <v>7264606</v>
+        <v>7264572</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2347,7 +2243,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2369,19 +2265,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115984554</v>
+        <v>115984559</v>
       </c>
       <c r="B17" t="n">
-        <v>90783</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2394,12 +2285,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2409,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>525188</v>
+        <v>525234</v>
       </c>
       <c r="R17" t="n">
-        <v>7264572</v>
+        <v>7264571</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2458,7 +2349,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2480,15 +2371,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115984458</v>
+        <v>115984514</v>
       </c>
       <c r="B18" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2496,21 +2382,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1588</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2520,10 +2406,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>525168</v>
+        <v>525095</v>
       </c>
       <c r="R18" t="n">
-        <v>7264635</v>
+        <v>7264593</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2569,7 +2455,7 @@
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>3419</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2591,37 +2477,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115984679</v>
+        <v>115984480</v>
       </c>
       <c r="B19" t="n">
-        <v>90337</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90692</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>1599</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2631,10 +2512,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>525214</v>
+        <v>525369</v>
       </c>
       <c r="R19" t="n">
-        <v>7264470</v>
+        <v>7264614</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2680,7 +2561,7 @@
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2702,37 +2583,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115984559</v>
+        <v>115984579</v>
       </c>
       <c r="B20" t="n">
-        <v>90783</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1209</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2742,10 +2618,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>525234</v>
+        <v>525543</v>
       </c>
       <c r="R20" t="n">
-        <v>7264571</v>
+        <v>7264552</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2791,7 +2667,7 @@
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2813,37 +2689,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115984544</v>
+        <v>115984492</v>
       </c>
       <c r="B21" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2853,10 +2724,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>525344</v>
+        <v>525382</v>
       </c>
       <c r="R21" t="n">
-        <v>7264579</v>
+        <v>7264606</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2902,7 +2773,7 @@
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>3455</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2924,37 +2795,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115984509</v>
+        <v>115984692</v>
       </c>
       <c r="B22" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>4769</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2830,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>525296</v>
+        <v>525147</v>
       </c>
       <c r="R22" t="n">
-        <v>7264594</v>
+        <v>7264464</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3013,7 +2879,7 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3035,37 +2901,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115984701</v>
+        <v>115984521</v>
       </c>
       <c r="B23" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3075,10 +2936,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>525240</v>
+        <v>525171</v>
       </c>
       <c r="R23" t="n">
-        <v>7264453</v>
+        <v>7264590</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3124,7 +2985,7 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3433</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3146,15 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115984553</v>
+        <v>115984544</v>
       </c>
       <c r="B24" t="n">
-        <v>91117</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3162,21 +3018,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>918</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3186,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>525220</v>
+        <v>525344</v>
       </c>
       <c r="R24" t="n">
-        <v>7264572</v>
+        <v>7264579</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3235,7 +3091,7 @@
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3257,37 +3113,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115984465</v>
+        <v>115984570</v>
       </c>
       <c r="B25" t="n">
-        <v>90624</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3297,10 +3148,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>525382</v>
+        <v>525525</v>
       </c>
       <c r="R25" t="n">
-        <v>7264626</v>
+        <v>7264567</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3346,7 +3197,7 @@
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3371,16 +3222,11 @@
         <v>115984690</v>
       </c>
       <c r="B26" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3479,50 +3325,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115984591</v>
+        <v>115984460</v>
       </c>
       <c r="B27" t="n">
-        <v>91117</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>918</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>525546</v>
+        <v>525225</v>
       </c>
       <c r="R27" t="n">
-        <v>7264537</v>
+        <v>7264633</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3557,6 +3403,11 @@
           <t>2022-09-22</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>färska hackmärken</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3568,7 +3419,7 @@
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3590,15 +3441,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115984560</v>
+        <v>115984707</v>
       </c>
       <c r="B28" t="n">
-        <v>90355</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3606,34 +3452,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>525217</v>
+        <v>525207</v>
       </c>
       <c r="R28" t="n">
-        <v>7264571</v>
+        <v>7264450</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3668,6 +3519,11 @@
           <t>2022-09-22</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3679,7 +3535,7 @@
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3701,50 +3557,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115984461</v>
+        <v>115984447</v>
       </c>
       <c r="B29" t="n">
-        <v>91117</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>918</v>
+        <v>100526</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tajgaskinn</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Laurilia sulcata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Burt) Pouzar</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>525246</v>
+        <v>525143</v>
       </c>
       <c r="R29" t="n">
-        <v>7264629</v>
+        <v>7264657</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3790,7 +3646,7 @@
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3812,15 +3668,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115984562</v>
+        <v>115984668</v>
       </c>
       <c r="B30" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3828,21 +3679,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3852,10 +3703,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>525234</v>
+        <v>525144</v>
       </c>
       <c r="R30" t="n">
-        <v>7264569</v>
+        <v>7264477</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3901,7 +3752,7 @@
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3923,15 +3774,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115984574</v>
+        <v>115984537</v>
       </c>
       <c r="B31" t="n">
-        <v>90359</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3939,34 +3785,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gejmån - Ajaure, Ly lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>525295</v>
+        <v>525477</v>
       </c>
       <c r="R31" t="n">
-        <v>7264563</v>
+        <v>7264582</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4012,7 +3862,7 @@
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>3453</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4027,117 +3877,6 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr">
-        <is>
-          <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>115984521</v>
-      </c>
-      <c r="B32" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Gejmån - Ajaure, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>525171</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7264590</v>
-      </c>
-      <c r="S32" t="n">
-        <v>5</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Storuman</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Tärna</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2022-09-22</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>3433</t>
-        </is>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Rickard Gustafsson</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Olle Kvarnbäck</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
         <is>
           <t>EEN0060 Hemavan - Kittelfjäll NVI</t>
         </is>
